--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_种族配置表_Manufacture_RaceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_种族配置表_Manufacture_RaceConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -350,7 +350,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,6 +360,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -680,7 +686,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -704,16 +710,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -722,91 +728,92 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1342,54 +1349,54 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>-0.01</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>0.01</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>0.07</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>0.07</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>0.01</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1446,54 +1453,54 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>0.05</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>-0.01</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>0.07</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>0.01</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>0.07</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>0.01</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2" t="s">
         <v>28</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_种族配置表_Manufacture_RaceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_种族配置表_Manufacture_RaceConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>种族ID</t>
   </si>
@@ -142,21 +142,6 @@
     <t>亡灵</t>
   </si>
   <si>
-    <t>Race_Dwarf</t>
-  </si>
-  <si>
-    <t>矮人</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>Race_Goblin</t>
-  </si>
-  <si>
-    <t>地精</t>
-  </si>
-  <si>
     <t>Race_Demon</t>
   </si>
   <si>
@@ -173,18 +158,6 @@
   </si>
   <si>
     <t>-0.03</t>
-  </si>
-  <si>
-    <t>Race_Beast</t>
-  </si>
-  <si>
-    <t>野兽</t>
-  </si>
-  <si>
-    <t>Race_Construct</t>
-  </si>
-  <si>
-    <t>构装体</t>
   </si>
 </sst>
 </file>
@@ -350,7 +323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,12 +333,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,7 +653,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -710,16 +677,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -728,92 +695,94 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1160,9 +1129,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1251,22 +1221,22 @@
       <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>-0.01</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>0.07</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>0.01</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1277,22 +1247,22 @@
       <c r="B5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>0.01</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>0.07</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1303,22 +1273,22 @@
       <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>0.07</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>0.07</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>0.01</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1329,179 +1299,75 @@
       <c r="B7" t="s">
         <v>35</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>0.05</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>0.07</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>0.01</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D8" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="F9" s="2">
         <v>0.01</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G9" s="2">
+        <v>0.01</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
         <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10">
-        <v>0.07</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10">
-        <v>0.07</v>
-      </c>
-      <c r="G10">
-        <v>0.01</v>
-      </c>
-      <c r="H10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11">
-        <v>0.01</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11">
-        <v>0.01</v>
-      </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
